--- a/news_push_data/master/cnyes_master.xlsx
+++ b/news_push_data/master/cnyes_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1955,6 +1955,1545 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>伊朗總統發表致美國民眾公開信：提美伊關係被誤解、並無敵意、非主動發動戰爭 | 鉅亨網 - 美股雷達</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-04-02 05:55</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-04-02T05:55:55+08:00</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405109</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>〈美股盤後〉FOMO情緒推升 三大指數連二升 台積電ADR續揚 | 鉅亨網 - 美股雷達</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-04-02 05:55</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-04-02T05:55:12+08:00</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405106</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>能源供應持續緊張！韓上調資源安全危機至三級 公家機關車輛改「單雙號限行」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-04-02 05:40</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-04-02T05:40:02+08:00</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404935</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>來硬的！UAE擬聯手美國 武力重開荷姆茲海峽 全球油市震盪 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-04-02 05:20</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-04-02T05:20:02+08:00</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405038</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>北約前景不明 馬克宏東京發言暗批川普：某國政策善變 傷害盟友 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-04-02 04:10</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-04-02T04:10:03+08:00</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405034</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>亞洲搶買俄油補戰爭缺口！菲律賓睽違6年首進口、南韓加入搶購行列 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-04-02 04:00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-04-02T04:00:07+08:00</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403581</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>運價飛天！亞洲國家瘋狂搶租美國油輪 日租金破30萬美元創史高 運費暴衝五倍 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-04-02 02:50</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-04-02T02:50:04+08:00</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405013</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>戴蒙談美伊戰爭：戰事成敗比市場波動更重要 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-04-02 02:30</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-04-02T02:30:03+08:00</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405064</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>資金大撤退！印度與台灣ETF創紀錄流出 市場情緒急轉 | 鉅亨網 - 美股雷達</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-04-02 02:00</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-04-02T02:00:03+08:00</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405039</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>伊朗否認停火說法 打臉川普稱「毫無根據」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-04-02 01:00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-04-02T01:00:05+08:00</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404962</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>不容外部勢力介入！伊朗外長：荷姆茲海峽的未來安排 將完全由伊朗與阿曼共同決定 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-04-02 00:10</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-04-02T00:10:02+08:00</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405015</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>再次打破傳統！美總統川普將出席最高法院針對「出生公民權」口頭辯論 | 鉅亨網 - 美股雷達</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-04-01 23:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-04-01T23:00:06+08:00</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404925</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>義大利小型衛星商Argotec佛州設廠 搶進美國衛星製造市場 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:30</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-04-01T21:30:04+08:00</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404865</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>川普稱伊朗提出停火 荷姆茲海峽未開放前不考慮 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:03</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-04-01T21:03:42+08:00</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404850</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>川普稱考慮退出NATO 不滿盟友未挺伊朗軍事行動 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:57</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-04-01T20:57:23+08:00</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404844</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>伊朗、真主黨、胡塞 再次聯合襲擊以色列 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-04-01 20:33</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-04-01T20:33:56+08:00</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404828</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>伊朗衝突外溢至美妝供應鏈，包材、運輸成本齊揚，業者示警終端售價恐上修 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-04-01T19:00:32+08:00</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404730</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>比亞迪3月銷量連七月下滑，年減逾兩成，中國車市價格戰壓力未解 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-04-01T19:00:31+08:00</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404729</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>德國7月起調降航空稅，短中長程機票稅負同步下修，航空業樂見但仍喊成本偏高 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-04-01T19:00:30+08:00</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404727</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>俄羅斯LNG首季出口年增近9%，歐洲進口反增17%，制裁下能源流向仍未脫鉤 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-04-01T19:00:29+08:00</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404726</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>一代人只見一次高點已過？彭博大宗商品分析師Mike McGlone：黃金白銀恐已見頂 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-04-01T18:00:02+08:00</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404180</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>不是漲停!就在漲停的路上!!鈦昇⊕、旺宏⊕、華通⊕、臻鼎、【四月神奇寶貝】開放免費索取 | 鉅亨網 - 專家觀點</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:39</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-04-01T17:39:42+08:00</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404612</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>美伊釋出停戰意願，台股融資大減百億後強勢反彈，底部訊號已明確？ | 鉅亨網 - 台股新聞</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:27</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-04-01T17:27:50+08:00</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404583</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>【量大強漲股整理】台股報復性反彈下，邁威爾獲輝達投資，潛力股大公開? | 鉅亨網 - 台股新聞</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:21</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-04-01T17:21:23+08:00</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404533</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>現代汽車3月南韓電動車銷量年增38%，首季國內新能源車銷售寫新高 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-04-01T16:00:07+08:00</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404408</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Alstom執行長由Martin Sion即刻接任，接棒推進全球軌道交通布局 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:30</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-04-01T15:30:05+08:00</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404385</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>美伊戰事衝擊供應鏈 日本煉油產能利用率下滑至 72.5% | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:30</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-04-01T15:30:04+08:00</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404384</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>VinFast損平時程延後至2027年後，2026年拚交車30萬輛 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-04-01T15:00:04+08:00</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404328</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>戴蒙出手拯救「美國夢」小摩供800億美元挺小企業與購屋 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-04-01T14:00:08+08:00</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403502</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>美軍中東戰損曝光：348人傷、預警機首度被毀、最強航母起火撤出戰場 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:16</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-04-01T13:16:36+08:00</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403906</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>美以伊第33天戰況：德黑蘭遇襲 胡塞飛彈又襲以色列 美伊有意停戰 盧比歐稱「已看到終點線」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:10</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-04-01T12:10:02+08:00</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403994</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>伊朗警告美軍基地「不再安全」 放話全面開打 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-04-01T12:00:07+08:00</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404033</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>盧比歐：沒有美國 北約將不復存在！赫格塞斯：川普將在對伊行動結束後就北約未來做決定 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:50</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-04-01T11:50:03+08:00</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404040</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>俄羅斯加速建構「Rassvet」衛星網路 對標Starlink、戰後商用布局同步浮現 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:30</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-04-01T11:30:08+08:00</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404124</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>川普釋出中東停火曙光帶動日經指數狂飆近 4%晶片與金融股領軍噴出 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-04-01T11:00:13+08:00</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404055</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>小米Xiaomi(1810-HK)電動車3月交付破2萬輛 產能爬坡邁入新階段 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-04-01T11:00:11+08:00</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404053</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>紐時專欄痛批：巨嬰玩火！川普誤判伊朗情勢 戰略恐引爆全球危機 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:00</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-04-01T11:00:07+08:00</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403872</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>行情不等人，資金已經開始卡位產業趨勢 | 鉅亨網 - 專家觀點</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:46</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-04-01T10:46:23+08:00</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>伊朗出動無人機 攻擊以色列西門子、AT&amp;T | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:44</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-04-01T10:44:22+08:00</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403903</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>美軍一架F-35隱形戰機墜毀 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:32</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-04-01T10:32:00+08:00</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403861</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>紐時：進攻還是防禦？英國首相如何決定美軍轟炸伊朗 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-04-01T10:00:51+08:00</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403927</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>華爾街日報：阿聯準備參戰 助美以武力打通荷姆茲海峽 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:58</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-04-01T09:58:33+08:00</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403836</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>【豐雲學堂ETF大賞】ETF怎麼配置才賺錢？5大類型差異一次講清楚！收益、債券、AI配置全解析 | 鉅亨網 - 台股新聞</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:05</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-04-01T09:05:00+08:00</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403656</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>無視中東衝突升級！韓3月出口額年增48.3%首破800億美元 半導體出口328億美元創史高 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-04-01T09:01:34+08:00</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403637</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>川普難以輕易抽身伊朗戰事 專家：荷姆茲海峽短期難恢復通行 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:49</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:49:11+08:00</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403631</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>伊朗宣布：關閉學生宿舍 所有課程轉線上教學 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:45</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:45:50+08:00</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403634</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>川普稱美國2至3週內可能結束對伊朗軍事行動戰事仍延燒伊朗揚言報復美企 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:30</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:30:07+08:00</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403614</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>伊拉克警方證實 美籍戰地女記者在巴格達遭擄 下落不明 川普政府高度關注 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:30</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:30:05+08:00</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403511</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>俄羅斯大使：伊朗最高領袖目前人在伊朗 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:29</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:29:46+08:00</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403583</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>川普表態：伊朗被打回「石器時代」就停戰 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:18</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:18:04+08:00</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403584</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>美海關退稅系統建置進度達60%至85% 4月底可望上線 審核流程最長45天 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:10</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-04-01T08:10:22+08:00</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403486</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>美伊透過中間人傳話 伊朗外長：收到美方訊息 但這不是談判 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:10</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-04-01T07:10:02+08:00</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403467</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>美軍布希號航母增援中東 區域將集結三航母打擊群 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:05</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-04-01T07:05:04+08:00</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403565</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>金融危機來最慘！國際金價3月跌幅創17年之最 但專家說還有翻身機會 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:00</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-04-01T07:00:06+08:00</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403245</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>國力大於鯨魚！美國「上帝小組」30年首開會 墨西哥灣油氣開採豁免瀕危物種法 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:50</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-04-01T06:50:04+08:00</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403389</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>中國、巴基斯坦提五點倡議 提到荷姆茲海峽 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:20</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-04-01T06:20:05+08:00</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403359</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>傳統記憶體估值下修不可避免！大摩：DDR4首當其衝 NAND廠商迎來高光時刻 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-04-01 06:10</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-04-01T06:10:03+08:00</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6400928</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/master/cnyes_master.xlsx
+++ b/news_push_data/master/cnyes_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3494,6 +3494,1545 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>川普政府公告對鋼鐵、鋁、銅衍生品徵25%關稅 | 鉅亨網 - 美股雷達</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-04-03 04:59</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-04-03T04:59:21+08:00</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406580</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>馬克宏批川普言論 恐削弱北約信任基礎 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-04-03 02:30</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-04-03T02:30:02+08:00</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406349</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>比高油價更傷！專家示警：財富縮水與「CNN效應」恐重挫美國經濟 | 鉅亨網 - 美股雷達</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-04-03 02:00</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-04-03T02:00:02+08:00</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405150</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>川普談話引爆油價壓力：美國汽油恐衝5美元、柴油逼近新高 | 鉅亨網 - 能源</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-04-03 01:00</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-04-03T01:00:05+08:00</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406515</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>川普政府擬對進口藥品課徵最高100%關稅 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-04-02 23:27</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-04-02T23:27:05+08:00</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406492</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>荷姆茲海峽有望恢復通行？伊朗與阿曼研擬監控機制 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-04-02 23:10</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-04-02T23:10:04+08:00</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406486</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>烏克蘭無人機狂襲 俄油港儲油設施損失四成 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-04-02 22:31</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-04-02T22:31:02+08:00</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406445</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>美上周初領失業金人數降至近兩年低點 就業市場陷「低招募、低裁員」 | 鉅亨網 - 美股雷達</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-04-02 22:00</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-04-02T22:00:03+08:00</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406268</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>〈美股早盤〉中東戰事降溫希望受挫 主要指數開低、油價勁揚 | 鉅亨網 - 美股雷達</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-04-02 21:42</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-04-02T21:42:03+08:00</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406266</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>油氣價格飆升 生質能源股成資金焦點 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-04-02 21:32</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-04-02T21:32:07+08:00</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406421</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>元太科技篤定入主台虹拿4席董事 陳永恒今以法人代表接任董事長 | 鉅亨網 - 台股新聞</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-04-02 21:14</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-04-02T21:14:36+08:00</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406395</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>國際油價暴衝10%！川普對伊朗強硬發言 點燃市場避險情緒 | 鉅亨網 - 能源</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-04-02 21:00</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-04-02T21:00:03+08:00</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406380</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>華爾街看中東戰事：川普談話未釋明確訊號 市場不確定性升溫 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-04-02 20:30</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-04-02T20:30:15+08:00</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406332</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>川普喊戰事將落幕 市場卻更怕高油價「吃掉需求」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-04-02 20:00</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-04-02T20:00:05+08:00</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406270</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>川普對伊朗戰事時間表含糊不清 引發市場與政治焦慮 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:50</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-04-02T19:50:02+08:00</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406235</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>禮來減重藥獲批、亞馬遜布局低軌衛星科技與醫療題材同步升溫 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:30</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-04-02T19:30:07+08:00</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406303</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>烏克蘭無人機打擊 俄羅斯石油出口受阻 減產壓力迫在眉睫 | 鉅亨網 - 能源</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:20</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-04-02T19:20:22+08:00</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406271</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>伊朗傳尋求中國安全擔保 北京呼籲美以停止軍事行動 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:50</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-04-02T18:50:03+08:00</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406189</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>【量大強漲股整理】清明變盤轉折出現?關鍵看甚麼?下周主流股就在這!!! | 鉅亨網 - 專家觀點</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:10</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-04-02T18:10:05+08:00</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406201</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>荷姆茲海峽局勢動盪 川普促亞洲自保 各國外交與能源策略現分歧 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:40</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-04-02T17:40:04+08:00</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405893</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>川普變數、清明長假雙重夾擊！台股回檔該跑還是加碼？ | 鉅亨網 - 台股新聞</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:31</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-04-02T17:31:41+08:00</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406109</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>節後才是大舉加碼最佳時機、華通9⊕、兆赫8⊕、鈦昇4⊕、下一檔【拳王鈦昇】請跟上 | 鉅亨網 - 專家觀點</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:22</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-04-02T17:22:21+08:00</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406055</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>史無前例的分裂言論！美媒：市場想聽的 川普一句都沒說 只是預告下一場風暴 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:10</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-04-02T17:10:03+08:00</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406023</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>川普揚言未來數週強攻伊朗中東股市早盤普遍走低、沙國逆勢收紅 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-04-02T17:00:05+08:00</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406032</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>回應川普演說 伊朗：絕不容忍戰爭、談判、停火的「惡性循環」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:40</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-04-02T16:40:04+08:00</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405997</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>實施『較低風險』的策略 獲利+10萬/2天！ | 鉅亨網 - 台股新聞</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:23</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-04-02T16:23:47+08:00</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405954</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>伊朗擊落16架「死神」無人機 美軍損失近4.8億美元 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:20</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-04-02T16:20:08+08:00</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405759</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>高盛重磅解讀「十五五」規劃：中國GDP鎖定4.4% 告別房地產依賴 點名四大賽道 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:20</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-04-02T16:20:04+08:00</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405754</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>每逢周四必定大跌 標普500已建立「戰爭模式」？ | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:18</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-04-02T16:18:04+08:00</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405848</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Krispy Kreme搭阿提米絲二號熱潮限時推聯名甜甜圈搶攻話題商機 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:31</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-04-02T15:31:27+08:00</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405909</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>川普揚言持續打擊伊朗全球股市重挫、油價衝破100美元 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:31</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-04-02T15:31:26+08:00</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405907</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>NASA發射阿提米絲二號睽違逾50年再啟載人繞月任務 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:31</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-04-02T15:31:26+08:00</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405905</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>專家：川普若「無協議」停戰 伊朗或成最後贏家 海灣國家陷戰略危局 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:20</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-04-02T15:20:05+08:00</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405788</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>4/10 CPI開獎有多慘? 通膨預期與遞延發酵才是重點 | 鉅亨網 - 專家觀點</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:58</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-04-02T13:58:26+08:00</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405770</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>民主黨怒轟川普演說「混亂可悲」 對伊朗戰略是史上最大失敗 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:57</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-04-02T13:57:52+08:00</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405756</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>油價飆升惹民怨！民調：川普經濟支持率降至31% 創任內新低 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:20</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-04-02T13:20:08+08:00</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405699</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>中東衝突成人民幣國際化破局之戰！德銀：石油美元面臨危機 人民幣迎來關鍵窗口期 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:20</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-04-02T13:20:04+08:00</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405195</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>美國低估伊朗？專家：伊朗戰爭恐比越戰更棘手 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:01</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-04-02T13:01:00+08:00</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405698</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>解放軍報披露：日本囤44.4噸分離鈽 夠製造5,500枚核彈頭 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:29</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-04-02T12:29:26+08:00</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405672</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>不排除地面戰、鎖海峽就重擊 川普演說全文、重點QA一次看 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:41</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-04-02T11:41:46+08:00</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405625</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>高盛：全球避險基金3月回檔幅度創四年多之最 亞洲避險基金暴跌7.3%最慘 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:40</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-04-02T11:40:06+08:00</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405209</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>最強救火隊集結！IEA、IMF、世銀發聯合聲明 將協調因應伊朗戰爭衝擊 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:21</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-04-02T11:21:32+08:00</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405459</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>伊朗最高領袖：繼續封鎖荷姆茲海峽 研究開闢潛在戰線 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:48</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:48:52+08:00</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405367</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>以色列擔憂美國宣布伊朗戰爭結束 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:32</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:32:17+08:00</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405354</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>英特爾Intel(INTC-US)斥資142億美元重掌Fab 34，AI推論需求升溫下強化歐洲晶圓廠控制權 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:30</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:30:07+08:00</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405521</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>川普暗示對伊朗採取進一步軍事打擊 亞太股市齊步由漲轉跌 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:25</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:25:16+08:00</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405508</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>美以伊衝突重塑全球液化天然氣貿易格局 澳洲迎千載難逢機會 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:00</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-04-02T10:00:13+08:00</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6404838</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>哈薩克：繼續向中國轉運俄羅斯原油 美國准了 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:54</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-04-02T09:54:31+08:00</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405219</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>川普發表演說 稱對伊朗戰爭取得壓倒性勝利 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:25</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-04-02T09:25:54+08:00</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405336</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>中東戰火延燒 成本壓力爆表 英國企業信心創6年最長跌勢 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:00</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-04-02T09:00:10+08:00</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405177</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>晶片再强也白搭？美AI資料中心建設潮遭遇「變壓器荒」 中國供應鏈卡住脖子 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:00</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-04-02T09:00:08+08:00</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6403979</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>供應告急！全球鋁庫存可用天數恐降至45天 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:35</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-04-02T08:35:57+08:00</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405196</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>尹錫悅看守所內「吸金」12億韓元 比李在明年薪高數倍 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:24</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-04-02T08:24:12+08:00</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405184</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>伊朗外交部：最高領袖身體健康 因戰爭推遲公開露面 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:15</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-04-02T08:15:37+08:00</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405183</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>川普：美軍「很快」就會撤離伊朗 但必要時仍會「點狀打擊」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:20</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-04-02T07:20:03+08:00</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405092</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>紐時：美軍增派18架A-10攻擊機 中東艦隊規模即將翻倍 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-04-02 06:52</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-04-02T06:52:34+08:00</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405107</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>伊朗最高領袖穆吉塔巴最新聲明：力挺真主黨 重申對抗「美以」立場 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-04-02 06:40</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-04-02T06:40:48+08:00</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6405133</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/master/cnyes_master.xlsx
+++ b/news_push_data/master/cnyes_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E171"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5033,6 +5033,600 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>《時代雜誌》政治、經濟、選舉壓力高！川普已經開始為伊朗戰爭尋找出路 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-04-03 22:00</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-04-03T22:00:03+08:00</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406957</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>報美國炸橋之仇！伊朗媒體稱將反擊「這些」目標 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-04-03 21:20</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-04-03T21:20:02+08:00</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406855</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>非農就業強勢反彈！3月新增17.8萬創近一年新高、Fed利率按兵不動機率99.5% | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-04-03 20:57</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-04-03T20:57:16+08:00</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406971</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>CNN曝衛星照！伊朗攻擊沙烏地美軍基地炸毀「薩德」雷達、E-3預警機 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-04-03 20:00</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-04-03T20:00:04+08:00</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406996</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>荷姆茲海峽僵局恐難解？聯合國安理會週末表決護航令、中俄法反對、內部分歧大 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:20</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-04-03T18:20:02+08:00</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406821</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>伊朗戰爭以來首艘西歐船隻！法國貨櫃船成功通過荷姆茲海峽 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:40</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-04-03T17:40:03+08:00</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406891</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>美國白打了？情報：伊朗約半數導彈發射裝置、數千架無人機「完好無損」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:10</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-04-03T17:10:05+08:00</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406840</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>荷姆茲海峽現「新跡象」！三艘掛阿曼旗的船隻疑似改走靠近阿曼海岸的「南線」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:04</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-04-03T16:04:36+08:00</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406820</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>美國在伊朗戰爭狂消耗「戰斧」庫存！日本400枚訂單交期拉警報 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:30</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-04-03T15:30:05+08:00</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406815</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>「影子艦隊」改道？載伊朗原油船疑「棄印投中」 2025年受美制裁身分曝光 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:20</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-04-03T15:20:02+08:00</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406607</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>美以伊開戰第34天戰況彙整：川普威脅加強打擊、葉門胡塞發動第四波導彈攻擊 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-04-03T15:00:02+08:00</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406822</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>私人信貸面臨嚴峻挑戰！專家警告：伊朗戰爭推高市場風險 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:10</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-04-03T14:10:03+08:00</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406777</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>川普威脅攻擊伊朗橋樑與發電廠！國際法專家警告美國或犯「戰爭罪」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-04-03 13:10</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-04-03T13:10:04+08:00</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406805</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>摩根大通示警：荷姆茲海峽封鎖若延至5月 油價恐飆上150美元 | 鉅亨網 - 能源</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-04-03 13:00</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-04-03T13:00:05+08:00</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406635</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>40國討論荷姆茲海峽 美國未被邀請引關注 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:46</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-04-03T12:46:51+08:00</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406744</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>川普解雇美國司法部長邦迪！不滿艾普斯坦案處理、起訴政敵太慢 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:20</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-04-03T12:20:10+08:00</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406773</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>伊朗已故國安首長胞弟：荷姆茲海峽不會回到戰前狀態 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-04-03 11:48</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-04-03T11:48:12+08:00</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406742</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>川普稱取得「壓倒性勝利」 伊朗回應！ | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-04-03 11:11</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-04-03T11:11:33+08:00</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406741</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>《外交事務》中東戰火重塑能源版圖 海灣國家轉向中國成新趨勢 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-04-03 10:00</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-04-03T10:00:11+08:00</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406557</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>西德州原油近四年首度超越布蘭特！如何解析價格反轉原因 | 鉅亨網 - 能源</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-04-03 09:30</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-04-03T09:30:09+08:00</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406662</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>「讓南韓來做啦！」川普不滿未出力護荷姆茲 駐軍問題再起 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-04-03 08:31</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-04-03T08:31:07+08:00</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406621</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>布蘭特原油現貨飆141美元、創2008年來新高！與期貨逆價差達32美元 | 鉅亨網 - 能源</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-04-03 08:10</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-04-03T08:10:03+08:00</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406625</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/master/cnyes_master.xlsx
+++ b/news_push_data/master/cnyes_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5627,6 +5627,303 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>川普再對伊朗下48小時最後通牒！伊朗強硬回應 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-04-04 23:11</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-04-04T23:11:32+08:00</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407446</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>巴克萊：伊朗鋼廠空襲衝擊有限、中東鋼材將加深依賴中國 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-04-04 21:00</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-04-04T21:00:02+08:00</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407363</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>美國大使館遭襲內幕曝！損害遠超公開預期、伊朗打擊能力強 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-04-04 19:00</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-04-04T19:00:10+08:00</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407345</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>川普推1.5兆美元國防預算創新高！削減教育、NASA與醫療支出引爭議 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-04-04 18:10</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-04-04T18:10:03+08:00</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407331</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>美國兩架戰機遭伊朗擊落！美軍F-15E與A-10戰機受損、搜救行動持續 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-04-04 16:00</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-04-04T16:00:03+08:00</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407263</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>《紐約客》批川普與赫格塞斯的伊朗戰爭構想「扭曲」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:00</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-04-04T15:00:04+08:00</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407262</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>美以伊開戰第35天戰況彙整：伊朗拒絕美國48小時停火建議、擊落美軍戰機 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-04-04T14:00:03+08:00</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407258</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>限制晶片設備出口中國！美國擬立新法 ASML舊款DUV恐也賣不了 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:10</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-04-04T12:10:04+08:00</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407108</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>《Politico》川普稱要再打伊朗「三週」引美軍官擔憂 撤軍怕丟臉、繼續恐難以抽身 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-04-04 11:10</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-04-04T11:10:04+08:00</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407104</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>伊朗首次擊落美國戰機！美軍展開搜救 飛行員被伊朗軍方俘虜？ | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-04-04 10:00</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-04-04T10:00:03+08:00</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407083</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>川普「解放日」關稅滿一週年！美國企業與消費者仍受政策不確定性影響 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-04-04 09:00</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-04-04T09:00:04+08:00</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406778</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/master/cnyes_master.xlsx
+++ b/news_push_data/master/cnyes_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E204"/>
+  <dimension ref="A1:E223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5924,6 +5924,519 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>韓國多地「垃圾袋荒」持續 垃圾袋成促銷爆品 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-04-05 23:15</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-04-05T23:15:25+08:00</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407746</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>川普將於週一舉行記者會！揭飛官救援更多細節、週末「不停工作」沒去海湖莊園 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:00</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-04-05T22:00:16+08:00</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407720</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>本週操盤筆記：美國3月CPI、Fed會議紀錄 | 鉅亨網 - 美股雷達</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-04-05 21:50</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-04-05T21:50:02+08:00</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406533</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>《經濟學人》伊朗戰爭演變成「亞洲危機」 面臨「三大挑戰」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-04-05 21:00</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-04-05T21:00:02+08:00</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407551</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>川普再次放話：4/7將是伊朗發電廠日、大橋日 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-04-05 20:58</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-04-05T20:58:53+08:00</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407714</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>持續換人止血？周三演說後未公開露面 傳川普正考慮大規模內閣改組 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-04-05 20:30</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-04-05T20:30:03+08:00</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407685</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>伊朗飛彈打擊為何如此精準？德國軍工防空專家曝關鍵 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-04-05 20:00</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-04-05T20:00:04+08:00</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407613</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>美軍機救援飛行員又遭擊落？伊朗宣稱擊中C-130、兩架「黑鷹」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-04-05 18:09</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-04-05T18:09:04+08:00</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407657</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>全球對中國認可度超越美國！蓋洛普民調：近20年領先幅度最大的一次 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-04-05 17:00</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-04-05T17:00:02+08:00</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407573</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>伊朗批准人道物資船通行荷姆茲海峽！擬推收費與分級制度 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-04-05 16:00</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-04-05T16:00:06+08:00</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407612</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>大摩預期Fed 2026降息劇本不變！油價飆漲只是噪音？ | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:00</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-04-05T15:00:04+08:00</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407549</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>美以伊開戰第36天戰況彙整：伊朗拒絕川普48小時最後通牒、美伊尋找F-15墜落飛行員 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-04-05 14:00</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-04-05T14:00:04+08:00</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407561</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>美軍遭伊朗擊落F-15E失蹤機組員獲救！川普發文：美國歷史上最大膽的搜救行動之一 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-04-05 12:30</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-04-05T12:30:07+08:00</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407576</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>美國「感到絕望」？伊朗媒體：美軍試圖炸死失聯飛行員 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-04-05 12:00</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-04-05T12:00:03+08:00</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407555</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>科威特石油總部遭無人機轟炸起火！伊朗擴大攻擊能源設施 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-04-05 11:00</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-04-05T11:00:02+08:00</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407546</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>全球原油庫存「這時」將見底！摩根大通算出「停擺時間表」 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-04-05 10:20</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-04-05T10:20:33+08:00</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407460</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>AI算力爆發加劇缺料，PCB上游與載板迎黃金期：欣興、台光電、金像電 | 鉅亨網 - 台股新聞</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-04-05 09:10</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-04-05T09:10:03+08:00</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406108</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>美國法官維持撤銷鮑爾刑事傳票裁決！Fed新主席確認或延遲 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-04-05 08:20</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-04-05T08:20:06+08:00</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6407459</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>伊朗聲稱擊落「第二架」美國F-35戰機：回應川普胡言亂語 | 鉅亨網 - 國際政經</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-04-03 19:14</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-04-03T19:14:50+08:00</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6406892</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
